--- a/Datos.xlsx
+++ b/Datos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pci\Documents\GitHub\Imagen-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5F7CBF-F154-4EE5-8488-26BE1722C987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB10783-01E1-4E32-A75F-C7732BC16234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4000D76-12C8-4C65-B235-B01DAADFA291}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="20760" windowHeight="11070" xr2:uid="{E4000D76-12C8-4C65-B235-B01DAADFA291}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t>Folio</t>
   </si>
@@ -112,16 +112,60 @@
   </si>
   <si>
     <t>Sí</t>
+  </si>
+  <si>
+    <t>Link_Antes</t>
+  </si>
+  <si>
+    <t>Link_Despues</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15x4OoKPGFMQrofSHee2gUBJUJsbwp6gQ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VF3Nm568QWuYe5GuXc1-Q3fKbKju_BH5/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1D7-cjLCZXOWRu7JXgxa3LapDH1UwJY-X/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZIuCiCKp5_ySneLHYbZASOvJYT6U_CI5/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1udPbi3aHVmCk7rOwsahnMTDTe1uwG_xt/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18KfAOtzYSvtHGeVQN26h2dy1qiE8-Pyj/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EqAb_P2tIXj9j14tc3fLqfwqtL84jbEc/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13_qDP6s70_ONkIdkB8X1Vj98KMgMA0rk/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1t5Y5FbFcGhz31PDPQrvARIBgAPWO2jUa/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19nLEGmFixIeet-evS1Mn_FSb33e3v_iO/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -144,13 +188,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -463,10 +510,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601F7C0-6C09-465A-90C2-30F2CEA07B63}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +544,14 @@
       <c r="J1" t="s">
         <v>3</v>
       </c>
+      <c r="K1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -526,8 +579,14 @@
       <c r="J2" t="s">
         <v>8</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -555,8 +614,14 @@
       <c r="J3" t="s">
         <v>8</v>
       </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -584,8 +649,14 @@
       <c r="J4">
         <v>0</v>
       </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -613,8 +684,14 @@
       <c r="J5">
         <v>0</v>
       </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -642,8 +719,17 @@
       <c r="J6">
         <v>0</v>
       </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{FF58429C-49AC-4A76-92DE-6B13AE51B6F0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Datos.xlsx
+++ b/Datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pci\Documents\GitHub\Imagen-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB10783-01E1-4E32-A75F-C7732BC16234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5665B89-D6D4-4321-927C-74728C6103EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="20760" windowHeight="11070" xr2:uid="{E4000D76-12C8-4C65-B235-B01DAADFA291}"/>
   </bookViews>
